--- a/output/pdf_financials_xlsx/TLA.xlsx
+++ b/output/pdf_financials_xlsx/TLA.xlsx
@@ -431,6 +431,15 @@
   </sheetPr>
   <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/TLA.xlsx
+++ b/output/pdf_financials_xlsx/TLA.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>3.41057</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2.689791</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>2.618424</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.00308</v>
+        <v>0.003249</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.003596</v>
+        <v>0.003889</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.003747</v>
+        <v>0.004056</v>
       </c>
     </row>
     <row r="11">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
@@ -10731,13 +10731,13 @@
         <v>2.618424</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>-0.003249</v>
+        <v>0.003249</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>-0.003889</v>
+        <v>0.003889</v>
       </c>
       <c r="J154" s="5" t="n">
-        <v>-0.004056</v>
+        <v>0.004056</v>
       </c>
     </row>
     <row r="155">

--- a/output/pdf_financials_xlsx/TLA.xlsx
+++ b/output/pdf_financials_xlsx/TLA.xlsx
@@ -1129,22 +1129,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.278699</v>
+        <v>0.374122</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.269169</v>
+        <v>0.368729</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.188204</v>
+        <v>0.277513</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.000174</v>
+        <v>0.000259</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.000196</v>
+        <v>0.000292</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.000208</v>
+        <v>0.000391</v>
       </c>
     </row>
     <row r="29">
@@ -1154,22 +1154,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.995632</v>
+        <v>-0.900209</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.605726</v>
+        <v>-0.506166</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.674545</v>
+        <v>0.763854</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.00039</v>
+        <v>-0.000305</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.000608</v>
+        <v>-0.000512</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.000313</v>
+        <v>-0.00013</v>
       </c>
     </row>
     <row r="30">
@@ -1179,22 +1179,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-24.22441658039408</v>
+        <v>-21.90270885771046</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-17.14177852538923</v>
+        <v>-14.32427445591268</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>15.58348819522671</v>
+        <v>17.64672452079061</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-6.276150627615062</v>
+        <v>-4.908271644673318</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-8.866851392737349</v>
+        <v>-7.466822225463031</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-4.634290790642582</v>
+        <v>-1.924785312407462</v>
       </c>
     </row>
     <row r="31">
@@ -2917,22 +2917,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.467151</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.458666</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.366059</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.000344</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.00038</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.000391</v>
       </c>
     </row>
     <row r="101">
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -6168,7 +6168,11 @@
           <t>Depreciation of property, plant and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -6210,7 +6214,11 @@
           <t>Depreciation of right-of-use assets (note 10)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6254,7 +6262,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7892,7 +7900,11 @@
           <t>Depreciation of property, plant and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -7936,7 +7948,11 @@
           <t>Depreciation of right-of-use assets (note 11)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -7982,7 +7998,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8710,7 +8726,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -8754,7 +8774,11 @@
           <t>Depreciation of right-of-use assets (note 8)</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -8800,7 +8824,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9446,7 +9470,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -9816,7 +9844,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>0.044286</v>
       </c>
@@ -9860,7 +9892,11 @@
           <t>Depreciation of right-of-use assets (note 8)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="n">
         <v>0.144166</v>
       </c>
@@ -9906,7 +9942,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -11536,7 +11572,11 @@
           <t>Depreciation of property, plant and equipment (notes 9 and 17)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -11553,10 +11593,10 @@
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>-3.3e-05</v>
+        <v>3.3e-05</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>-3.6e-05</v>
+        <v>3.6e-05</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -11580,7 +11620,11 @@
           <t>Depreciation of right-of-use assets (notes 10 and 17)</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -11597,10 +11641,10 @@
         </is>
       </c>
       <c r="H174" s="5" t="n">
-        <v>-5.2e-05</v>
+        <v>5.2e-05</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>-6e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -11626,7 +11670,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11645,10 +11689,10 @@
         </is>
       </c>
       <c r="H175" s="5" t="n">
-        <v>-0.000174</v>
+        <v>0.000174</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>-0.000196</v>
+        <v>0.000196</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -12522,7 +12566,11 @@
           <t>Depreciation of property, plant and equipment (notes 10 and 20)</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -12566,7 +12614,11 @@
           <t>Depreciation of right-of-use assets (notes 11 and 20)</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -12612,7 +12664,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -13386,7 +13438,11 @@
           <t>Depreciation of property, plant and equipment (notes 7 and 18)</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -13430,7 +13486,11 @@
           <t>Depreciation of right-of-use assets (notes 8 and 18)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -13476,7 +13536,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13982,7 +14042,11 @@
           <t>Depreciation of property, plant and equipment (notes 7 and 17)</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E227" s="5" t="n">
         <v>0.027959</v>
       </c>
@@ -14026,7 +14090,11 @@
           <t>Depreciation of right-of-use assets (notes 8 and 17)</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E228" s="5" t="n">
         <v>0.067464</v>
       </c>
@@ -14072,7 +14140,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">

--- a/output/pdf_financials_xlsx/TLA.xlsx
+++ b/output/pdf_financials_xlsx/TLA.xlsx
@@ -836,10 +836,10 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.000634</v>
+        <v>-0.000634</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-8.500000000000001e-05</v>
       </c>
     </row>
     <row r="18">
@@ -937,10 +937,8 @@
       <c r="F20" s="3" t="n">
         <v>0.000546</v>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>-0.000606</v>
       </c>
     </row>
     <row r="21">
@@ -1015,7 +1013,7 @@
         <v>0.000546</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.000521</v>
+        <v>-0.000606</v>
       </c>
     </row>
     <row r="24">
@@ -1094,7 +1092,7 @@
         <v>0.0273</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.02605</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="27">
@@ -1219,7 +1217,7 @@
         <v>-720.4545454545454</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-16.3147792706334</v>
       </c>
     </row>
     <row r="32">
@@ -1244,7 +1242,7 @@
         <v>7.962665888872684</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-7.713947290494522</v>
+        <v>-8.972460763991709</v>
       </c>
     </row>
     <row r="33">
@@ -1411,22 +1409,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.239311</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.062945</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.06422</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.000446</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.000232</v>
       </c>
     </row>
     <row r="41">
@@ -1436,22 +1434,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.606719</v>
+        <v>0.8460299999999999</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.7300720000000001</v>
+        <v>0.793017</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.833508</v>
+        <v>0.897728</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.000936</v>
+        <v>0.001035</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.001345</v>
+        <v>0.001791</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.000961</v>
+        <v>0.001193</v>
       </c>
     </row>
     <row r="42">
@@ -1611,22 +1609,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.501712</v>
+        <v>0.262401</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.427789</v>
+        <v>0.364844</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.63897</v>
+        <v>1.57475</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.001366</v>
+        <v>0.001267</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.000915</v>
+        <v>0.000469</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000448</v>
+        <v>0.000216</v>
       </c>
     </row>
     <row r="49">
@@ -2023,22 +2021,22 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.199234</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.099054</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.384878</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.000384</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.000431</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.000568</v>
       </c>
     </row>
     <row r="65">
@@ -2173,22 +2171,22 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.13085</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.130203</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.136415</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.000133</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.000143</v>
       </c>
     </row>
     <row r="71">
@@ -2198,22 +2196,22 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.13085</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.130203</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.136415</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.000133</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.000143</v>
       </c>
     </row>
     <row r="72">
@@ -2298,22 +2296,22 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.131638</v>
+        <v>0.000788</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.14347</v>
+        <v>0.013267</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.146795</v>
+        <v>0.01038</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.000102</v>
+        <v>6e-06</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.000185</v>
+        <v>5.2e-05</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.000143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2373,22 +2371,22 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>0.38394</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>0.253736</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>0.117321</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>0.000681</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>0.000457</v>
       </c>
     </row>
     <row r="79">
@@ -2398,22 +2396,22 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>0.38394</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>0.253736</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>0.117321</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>0.000681</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0</v>
+        <v>0.000457</v>
       </c>
     </row>
     <row r="80">
@@ -2422,35 +2420,23 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.03265331960615576</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.02470973992599544</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.01519529835421198</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.04603626022040526</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.04188092789395498</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.03656307129798903</v>
       </c>
     </row>
     <row r="81">
@@ -2560,22 +2546,22 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>0.38394</v>
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0.253736</v>
+        <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.117321</v>
+        <v>0</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.000682</v>
+        <v>1e-06</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.000457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2907,7 +2893,7 @@
         <v>0.000546</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-0.000521</v>
+        <v>-0.000606</v>
       </c>
     </row>
     <row r="100">
@@ -3273,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.77125</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
@@ -3307,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.000283</v>
       </c>
     </row>
     <row r="116">
@@ -3457,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.000759</v>
       </c>
     </row>
     <row r="122">
@@ -4556,7 +4542,11 @@
           <t>Current portion of lease obligations (note 13)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4634,7 +4624,11 @@
           <t>Lease obligations (note 13)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -5344,7 +5338,11 @@
           <t>Current portion of lease obligations (note 15)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5388,7 +5386,11 @@
           <t>Lease obligations (note 15)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -5994,7 +5996,11 @@
           <t>Current portion of lease obligations (note 12)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.13085</v>
       </c>
@@ -6038,7 +6044,11 @@
           <t>Lease obligations (note 12)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.38394</v>
       </c>
@@ -6532,7 +6542,11 @@
           <t>Deferred tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -6756,7 +6770,11 @@
           <t>Proceeds on sale of marketable securities (note 7)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -7030,7 +7048,11 @@
           <t>Repurchase of common shares (note 15)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -8454,7 +8476,11 @@
           <t>Purchase of marketable securities (note 8)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -9378,7 +9404,11 @@
           <t>Purchase of marketable securities (note 10)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -11000,7 +11030,11 @@
           <t>Income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
